--- a/03_Outputs/De_la_Paz/08_Educacion/educacion.xlsx
+++ b/03_Outputs/De_la_Paz/08_Educacion/educacion.xlsx
@@ -3311,13 +3311,13 @@
         <v>2021</v>
       </c>
       <c r="F88" s="7">
-        <v>0.781685452484999</v>
+        <v>0.898374584145499</v>
       </c>
       <c r="G88" s="9">
-        <v>0.0365894431037481</v>
+        <v>0.0457962595026783</v>
       </c>
       <c r="H88" s="11">
-        <v>0.0201105846704061</v>
+        <v>0.061110584216439</v>
       </c>
     </row>
     <row r="89">
@@ -3345,13 +3345,13 @@
         <v>2021</v>
       </c>
       <c r="F89" s="7">
-        <v>0.808399619674067</v>
+        <v>0.924418856993982</v>
       </c>
       <c r="G89" s="9">
-        <v>0.0340611041845194</v>
+        <v>0.0471531226376282</v>
       </c>
       <c r="H89" s="11">
-        <v>0.0537186135094694</v>
+        <v>0.0582136438740334</v>
       </c>
     </row>
     <row r="90">
